--- a/Team-Data/2012-13/1-10-2012-13.xlsx
+++ b/Team-Data/2012-13/1-10-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -796,13 +863,13 @@
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
       </c>
       <c r="AY2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
         <v>2</v>
@@ -811,7 +878,7 @@
         <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -933,7 +1000,7 @@
         <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI3" t="n">
         <v>15</v>
@@ -954,13 +1021,13 @@
         <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
         <v>29</v>
@@ -990,7 +1057,7 @@
         <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>11</v>
@@ -1148,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>15</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>28</v>
@@ -1336,7 +1403,7 @@
         <v>17</v>
       </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV5" t="n">
         <v>7</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>1.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>8</v>
@@ -1488,7 +1555,7 @@
         <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1503,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
@@ -1512,7 +1579,7 @@
         <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1749,7 @@
         <v>11</v>
       </c>
       <c r="AO7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
         <v>16</v>
@@ -1703,7 +1770,7 @@
         <v>30</v>
       </c>
       <c r="AV7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
         <v>11</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -1753,100 +1820,100 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>0.378</v>
+        <v>0.361</v>
       </c>
       <c r="H8" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="I8" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J8" t="n">
-        <v>83.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M8" t="n">
         <v>19.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="O8" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="P8" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.791</v>
+        <v>0.788</v>
       </c>
       <c r="R8" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T8" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="U8" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W8" t="n">
         <v>7.8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>98.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.3</v>
+        <v>-4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>21</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
         <v>5</v>
@@ -1864,19 +1931,19 @@
         <v>15</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR8" t="n">
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT8" t="n">
         <v>20</v>
@@ -1885,28 +1952,28 @@
         <v>17</v>
       </c>
       <c r="AV8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
         <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BB8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -2016,13 +2083,13 @@
         <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
         <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>23</v>
@@ -2046,7 +2113,7 @@
         <v>27</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
         <v>6</v>
@@ -2067,7 +2134,7 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW9" t="n">
         <v>13</v>
@@ -2085,7 +2152,7 @@
         <v>3</v>
       </c>
       <c r="BB9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
         <v>8</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -2195,13 +2262,13 @@
         <v>-1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
         <v>23</v>
@@ -2228,7 +2295,7 @@
         <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2240,13 +2307,13 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
         <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -2377,13 +2444,13 @@
         <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG11" t="n">
         <v>7</v>
@@ -2407,10 +2474,10 @@
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
         <v>17</v>
@@ -2446,7 +2513,7 @@
         <v>27</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>2.8</v>
       </c>
       <c r="AD12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE12" t="n">
         <v>8</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>9</v>
       </c>
       <c r="AF12" t="n">
         <v>11</v>
@@ -2571,7 +2638,7 @@
         <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2601,7 +2668,7 @@
         <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
         <v>5</v>
@@ -2625,10 +2692,10 @@
         <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -2663,61 +2730,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
         <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.611</v>
+        <v>0.6</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="J13" t="n">
         <v>80.8</v>
       </c>
       <c r="K13" t="n">
-        <v>0.42</v>
+        <v>0.421</v>
       </c>
       <c r="L13" t="n">
         <v>6.4</v>
       </c>
       <c r="M13" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O13" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R13" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S13" t="n">
         <v>33.3</v>
       </c>
       <c r="T13" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="U13" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W13" t="n">
         <v>6.5</v>
@@ -2732,19 +2799,19 @@
         <v>19.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>90.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AD13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE13" t="n">
         <v>8</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>8</v>
@@ -2753,7 +2820,7 @@
         <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2765,16 +2832,16 @@
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
@@ -2786,16 +2853,16 @@
         <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2804,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
         <v>13</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2956,7 +3023,7 @@
         <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2989,13 +3056,13 @@
         <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>19</v>
@@ -3117,7 +3184,7 @@
         <v>19</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>5.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3299,7 +3366,7 @@
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI16" t="n">
         <v>20</v>
@@ -3308,7 +3375,7 @@
         <v>15</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,13 +3384,13 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -3341,7 +3408,7 @@
         <v>20</v>
       </c>
       <c r="AV16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3350,13 +3417,13 @@
         <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -3391,94 +3458,94 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E17" t="n">
         <v>23</v>
       </c>
       <c r="F17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>0.676</v>
+        <v>0.697</v>
       </c>
       <c r="H17" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J17" t="n">
         <v>78</v>
       </c>
       <c r="K17" t="n">
-        <v>0.487</v>
+        <v>0.488</v>
       </c>
       <c r="L17" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M17" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.392</v>
+        <v>0.394</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P17" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R17" t="n">
         <v>8</v>
       </c>
       <c r="S17" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T17" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="U17" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V17" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W17" t="n">
         <v>8</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
         <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>101.8</v>
+        <v>102.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
       </c>
       <c r="AF17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
         <v>13</v>
@@ -3502,19 +3569,19 @@
         <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AT17" t="n">
         <v>29</v>
@@ -3529,7 +3596,7 @@
         <v>14</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,10 +3605,10 @@
         <v>7</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
         <v>6</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3663,7 +3730,7 @@
         <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
         <v>13</v>
@@ -3687,7 +3754,7 @@
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ18" t="n">
         <v>17</v>
@@ -3720,10 +3787,10 @@
         <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4069,7 +4136,7 @@
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -4119,70 +4186,70 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
         <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.657</v>
+        <v>0.676</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="J21" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.446</v>
+        <v>0.449</v>
       </c>
       <c r="L21" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="M21" t="n">
-        <v>29</v>
+        <v>29.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.386</v>
+        <v>0.39</v>
       </c>
       <c r="O21" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P21" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="Q21" t="n">
         <v>0.75</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T21" t="n">
-        <v>40.3</v>
+        <v>40</v>
       </c>
       <c r="U21" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="V21" t="n">
         <v>11.1</v>
       </c>
       <c r="W21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="X21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z21" t="n">
         <v>18.9</v>
@@ -4191,13 +4258,13 @@
         <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>101.5</v>
+        <v>102.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -4212,10 +4279,10 @@
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK21" t="n">
         <v>12</v>
@@ -4227,34 +4294,34 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AQ21" t="n">
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS21" t="n">
         <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4269,7 +4336,7 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
         <v>5</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4406,7 +4473,7 @@
         <v>10</v>
       </c>
       <c r="AM22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>-3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG23" t="n">
         <v>25</v>
@@ -4579,13 +4646,13 @@
         <v>8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
       </c>
       <c r="AL23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -4761,10 +4828,10 @@
         <v>16</v>
       </c>
       <c r="AJ24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
         <v>19</v>
@@ -4791,7 +4858,7 @@
         <v>18</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU24" t="n">
         <v>19</v>
@@ -4806,7 +4873,7 @@
         <v>16</v>
       </c>
       <c r="AY24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4818,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="BC24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -4937,7 +5004,7 @@
         <v>26</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI25" t="n">
         <v>7</v>
@@ -4973,7 +5040,7 @@
         <v>28</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -5029,43 +5096,43 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F26" t="n">
         <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>0.571</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>48.9</v>
       </c>
       <c r="I26" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.438</v>
+        <v>0.44</v>
       </c>
       <c r="L26" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O26" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P26" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q26" t="n">
         <v>0.771</v>
@@ -5074,61 +5141,61 @@
         <v>11.9</v>
       </c>
       <c r="S26" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U26" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V26" t="n">
         <v>14.6</v>
       </c>
       <c r="W26" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X26" t="n">
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z26" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AA26" t="n">
         <v>19</v>
       </c>
-      <c r="AA26" t="n">
-        <v>19.1</v>
-      </c>
       <c r="AB26" t="n">
-        <v>97.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AD26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE26" t="n">
         <v>13</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>11</v>
       </c>
       <c r="AF26" t="n">
         <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
       </c>
       <c r="AI26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="n">
         <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5140,22 +5207,22 @@
         <v>23</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ26" t="n">
         <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU26" t="n">
         <v>22</v>
@@ -5164,7 +5231,7 @@
         <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX26" t="n">
         <v>21</v>
@@ -5173,7 +5240,7 @@
         <v>5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA26" t="n">
         <v>23</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -5211,106 +5278,106 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" t="n">
         <v>13</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.361</v>
+        <v>0.371</v>
       </c>
       <c r="H27" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J27" t="n">
         <v>83.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L27" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M27" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.35</v>
+        <v>0.353</v>
       </c>
       <c r="O27" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P27" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="Q27" t="n">
         <v>0.768</v>
       </c>
       <c r="R27" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="T27" t="n">
         <v>40.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V27" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W27" t="n">
         <v>8.1</v>
       </c>
       <c r="X27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y27" t="n">
         <v>6.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="AC27" t="n">
         <v>-5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH27" t="n">
         <v>22</v>
       </c>
-      <c r="AF27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>16</v>
-      </c>
       <c r="AI27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
         <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>16</v>
@@ -5319,19 +5386,19 @@
         <v>15</v>
       </c>
       <c r="AN27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AP27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>30</v>
@@ -5343,13 +5410,13 @@
         <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW27" t="n">
         <v>12</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY27" t="n">
         <v>26</v>
@@ -5358,10 +5425,10 @@
         <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -5501,10 +5568,10 @@
         <v>6</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
@@ -5516,7 +5583,7 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT28" t="n">
         <v>19</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -5653,19 +5720,19 @@
         <v>-2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="n">
         <v>20</v>
       </c>
       <c r="AG29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI29" t="n">
         <v>22</v>
@@ -5683,10 +5750,10 @@
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
         <v>13</v>
@@ -5698,7 +5765,7 @@
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5713,7 +5780,7 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
@@ -5722,10 +5789,10 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5905,7 @@
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5847,7 +5914,7 @@
         <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI30" t="n">
         <v>17</v>
@@ -5874,7 +5941,7 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>6</v>
@@ -5907,7 +5974,7 @@
         <v>8</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-8</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6035,7 +6102,7 @@
         <v>29</v>
       </c>
       <c r="AJ31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6062,7 +6129,7 @@
         <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
         <v>7</v>
@@ -6071,13 +6138,13 @@
         <v>23</v>
       </c>
       <c r="AV31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW31" t="n">
         <v>24</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-10-2012-13</t>
+          <t>2013-01-10</t>
         </is>
       </c>
     </row>
